--- a/data/Collaborator data/Sample_data_sheet_uplb_philippines.xlsx
+++ b/data/Collaborator data/Sample_data_sheet_uplb_philippines.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/Collaborator data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0743903-3ED7-9443-A34A-3FB2A4BDE067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBD5A679-4737-AF4B-A6CF-60BA661D0B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16300" xr2:uid="{B33CD5FD-8344-D041-B682-A5C54B7EB73E}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1591" uniqueCount="286">
   <si>
     <t>speciesID</t>
   </si>
@@ -308,6 +308,591 @@
   </si>
   <si>
     <t>Microtarsus  urostictus</t>
+  </si>
+  <si>
+    <t>MNH 3764</t>
+  </si>
+  <si>
+    <t>Moralde, Ma. Patricia Marielle</t>
+  </si>
+  <si>
+    <t>MNH 3762</t>
+  </si>
+  <si>
+    <t>30.6 g</t>
+  </si>
+  <si>
+    <t>MNH 3759</t>
+  </si>
+  <si>
+    <t>32.9 g</t>
+  </si>
+  <si>
+    <t>MNH 3755</t>
+  </si>
+  <si>
+    <t>Malabusog, Tinitian, Palawan Island</t>
+  </si>
+  <si>
+    <t>31.6 g</t>
+  </si>
+  <si>
+    <t>MNH 3754</t>
+  </si>
+  <si>
+    <t>Macagua, Mantalingahan Range, Brooke's Point, Palawan Island</t>
+  </si>
+  <si>
+    <t>32.5 g</t>
+  </si>
+  <si>
+    <t>MNH 3752</t>
+  </si>
+  <si>
+    <t>Yellow-wattled Bulbul</t>
+  </si>
+  <si>
+    <t>MNH 3745</t>
+  </si>
+  <si>
+    <t>Tambo, Munai, Lanao del Norte, Mindanao Island</t>
+  </si>
+  <si>
+    <t>philippensis</t>
+  </si>
+  <si>
+    <t>25.2 g</t>
+  </si>
+  <si>
+    <t>MNH 3744</t>
+  </si>
+  <si>
+    <t>21.2 g</t>
+  </si>
+  <si>
+    <t>MNH 3743</t>
+  </si>
+  <si>
+    <t>26.8 g</t>
+  </si>
+  <si>
+    <t>MNH 3742</t>
+  </si>
+  <si>
+    <t>Datal-Bukay, Mt. Tuduk, Glan, Cotabato, Mindanao Island</t>
+  </si>
+  <si>
+    <t>28.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3737</t>
+  </si>
+  <si>
+    <t>Kibawalan, Malalag, Davao Province, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3736</t>
+  </si>
+  <si>
+    <t>Talagutong, Malita, Davao Province, Mindanao Island</t>
+  </si>
+  <si>
+    <t>23.9 g</t>
+  </si>
+  <si>
+    <t>MNH 3735</t>
+  </si>
+  <si>
+    <t>MNH 3729</t>
+  </si>
+  <si>
+    <t>MNH 3728</t>
+  </si>
+  <si>
+    <t>MNH 3727</t>
+  </si>
+  <si>
+    <t>MNH 3726</t>
+  </si>
+  <si>
+    <t>Diway, Dabiak, Zamboanga, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3274</t>
+  </si>
+  <si>
+    <t>Balang-Balang, Cabadbaran, Mt. Hilong-hilong, Agusan, Mindanao Island</t>
+  </si>
+  <si>
+    <t>Microtarsus urostictus</t>
+  </si>
+  <si>
+    <t>Pycnonotus plumosus</t>
+  </si>
+  <si>
+    <t>MNH 3763</t>
+  </si>
+  <si>
+    <t>Macagua, Brooke's Point, Palawan Province, Palawan Island</t>
+  </si>
+  <si>
+    <t>cinereifrons</t>
+  </si>
+  <si>
+    <t>Abacahin, Venus Nadine J.</t>
+  </si>
+  <si>
+    <t>Buenavista, Sabong, Palawan Province</t>
+  </si>
+  <si>
+    <t>MNH 3760</t>
+  </si>
+  <si>
+    <t>MNH 3756</t>
+  </si>
+  <si>
+    <t>Malabusog, Tinitian, Roxas, Palawan Province</t>
+  </si>
+  <si>
+    <t>MNH 3753</t>
+  </si>
+  <si>
+    <t>MNH 3746</t>
+  </si>
+  <si>
+    <t>MNH 3747</t>
+  </si>
+  <si>
+    <t>23.1 g</t>
+  </si>
+  <si>
+    <t>MNH 3748</t>
+  </si>
+  <si>
+    <t>Tagbalogo, Naawan, Misamis Oriental, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3749</t>
+  </si>
+  <si>
+    <t>34.6 g</t>
+  </si>
+  <si>
+    <t>MNH 3750</t>
+  </si>
+  <si>
+    <t>32.3 g</t>
+  </si>
+  <si>
+    <t>MNH 3738</t>
+  </si>
+  <si>
+    <t>Kibawalan, Malalag, Davao del Norte, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3739</t>
+  </si>
+  <si>
+    <t>MNH 3740</t>
+  </si>
+  <si>
+    <t>MNH 3741</t>
+  </si>
+  <si>
+    <t>MNH 3730</t>
+  </si>
+  <si>
+    <t>MNH 3731</t>
+  </si>
+  <si>
+    <t>Talagutong, Malita, Davao Occidental, Mindanao Island</t>
+  </si>
+  <si>
+    <t>25.3 g</t>
+  </si>
+  <si>
+    <t>MNH 3732</t>
+  </si>
+  <si>
+    <t>23.5 g</t>
+  </si>
+  <si>
+    <t>MNH 3733</t>
+  </si>
+  <si>
+    <t>22.8 g</t>
+  </si>
+  <si>
+    <t>MNH 3734</t>
+  </si>
+  <si>
+    <t>MNH 3725</t>
+  </si>
+  <si>
+    <t>Balangbalang, Cabadbaran, Mt. Hilong-hilong, Agusan del Norte, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3723</t>
+  </si>
+  <si>
+    <t>27.2 g</t>
+  </si>
+  <si>
+    <t>No; Poliolophus urostictus</t>
+  </si>
+  <si>
+    <t>MNH 3707</t>
+  </si>
+  <si>
+    <t>Camp Dungue, Tuod, Manticao, Misamis Oriental, Mindanao Island</t>
+  </si>
+  <si>
+    <t>DS Rabor</t>
+  </si>
+  <si>
+    <t>Gonzalez, Juan Carlos T.</t>
+  </si>
+  <si>
+    <t>MNH 3708</t>
+  </si>
+  <si>
+    <t>broken bill tip</t>
+  </si>
+  <si>
+    <t>MNH 3709</t>
+  </si>
+  <si>
+    <t>Mahayhay, Ma-nit, Iligan City, Lanao del Norte, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3710</t>
+  </si>
+  <si>
+    <t>MNH 3711</t>
+  </si>
+  <si>
+    <t>MNH 3713</t>
+  </si>
+  <si>
+    <t>MNH 3714</t>
+  </si>
+  <si>
+    <t>MNH 3715</t>
+  </si>
+  <si>
+    <t>MNH 3716</t>
+  </si>
+  <si>
+    <t>MNH 3717</t>
+  </si>
+  <si>
+    <t>MNH 3718</t>
+  </si>
+  <si>
+    <t>2 June 19678</t>
+  </si>
+  <si>
+    <t>MNH 3719</t>
+  </si>
+  <si>
+    <t>MNH 3721</t>
+  </si>
+  <si>
+    <t>Balangbalang, Cabadbaran, Mt Hilong-hilong, Agusan, Mindanao Island</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>25.4 g; broken bill</t>
+  </si>
+  <si>
+    <t>MNH 3722</t>
+  </si>
+  <si>
+    <t>27.3 g</t>
+  </si>
+  <si>
+    <t>MNH 3700</t>
+  </si>
+  <si>
+    <t>MNH 3701</t>
+  </si>
+  <si>
+    <t>23.4 g</t>
+  </si>
+  <si>
+    <t>MNH 3702</t>
+  </si>
+  <si>
+    <t>20.5 g</t>
+  </si>
+  <si>
+    <t>MNH 3703</t>
+  </si>
+  <si>
+    <t>25.5 g</t>
+  </si>
+  <si>
+    <t>MNH 3704</t>
+  </si>
+  <si>
+    <t>19.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3705</t>
+  </si>
+  <si>
+    <t>MNH 3706</t>
+  </si>
+  <si>
+    <t>MNH 3691</t>
+  </si>
+  <si>
+    <t>30 Junj 1965</t>
+  </si>
+  <si>
+    <t>Mt. Mayo, Limot, Mati, Davao Prov., Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3692</t>
+  </si>
+  <si>
+    <t>25.8 g</t>
+  </si>
+  <si>
+    <t>MNH 3693</t>
+  </si>
+  <si>
+    <t>18.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3694</t>
+  </si>
+  <si>
+    <t>13.1 g</t>
+  </si>
+  <si>
+    <t>MNH 3695</t>
+  </si>
+  <si>
+    <t>24.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3696</t>
+  </si>
+  <si>
+    <t>26 g</t>
+  </si>
+  <si>
+    <t>MNH 3697</t>
+  </si>
+  <si>
+    <t>24.2 g</t>
+  </si>
+  <si>
+    <t>MNH 3698</t>
+  </si>
+  <si>
+    <t>23.25 g</t>
+  </si>
+  <si>
+    <t>MNH 3699</t>
+  </si>
+  <si>
+    <t>30.2 g</t>
+  </si>
+  <si>
+    <t>MNH 3690</t>
+  </si>
+  <si>
+    <t>MNH 3689</t>
+  </si>
+  <si>
+    <t>25.14 g</t>
+  </si>
+  <si>
+    <t>MNH 3688</t>
+  </si>
+  <si>
+    <t>MNH 3687</t>
+  </si>
+  <si>
+    <t>Kibawalan, Malalag, Davao Prov., Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3686</t>
+  </si>
+  <si>
+    <t>Talagutong, Malita, Davao Prov., Midndanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3685</t>
+  </si>
+  <si>
+    <t>26.6 g</t>
+  </si>
+  <si>
+    <t>MNH 3684</t>
+  </si>
+  <si>
+    <t>DS Rabor; bill broken tip</t>
+  </si>
+  <si>
+    <t>MNH 3683</t>
+  </si>
+  <si>
+    <t>26.8 g; bill broken tip</t>
+  </si>
+  <si>
+    <t>MNH 3682</t>
+  </si>
+  <si>
+    <t>MNH 3681</t>
+  </si>
+  <si>
+    <t>MNH 3680</t>
+  </si>
+  <si>
+    <t>MNH 3679</t>
+  </si>
+  <si>
+    <t>MNH 3678</t>
+  </si>
+  <si>
+    <t>MNH 3677</t>
+  </si>
+  <si>
+    <t>MNH 3675</t>
+  </si>
+  <si>
+    <t>Sibahay, Lanuza, Surigao del Sur, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3673</t>
+  </si>
+  <si>
+    <t>Balangbalang, Cabadbaran, Mt. Hilong-hilong, Agusan, Mindanao Island</t>
+  </si>
+  <si>
+    <t>27.17 g</t>
+  </si>
+  <si>
+    <t>MNH 3672</t>
+  </si>
+  <si>
+    <t>27.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3674</t>
+  </si>
+  <si>
+    <t>Siwod, Mt Hilong-Hilong, Agusan Province, Mindanao Island</t>
+  </si>
+  <si>
+    <t>30.5 g</t>
+  </si>
+  <si>
+    <t>MNH 3671</t>
+  </si>
+  <si>
+    <t>MNH 3670</t>
+  </si>
+  <si>
+    <t>MNH 3669</t>
+  </si>
+  <si>
+    <t>26.54 g</t>
+  </si>
+  <si>
+    <t>MNH 3668</t>
+  </si>
+  <si>
+    <t>27.27 g</t>
+  </si>
+  <si>
+    <t>Mt Mayo, Limot, Mati, Davao Prov., Mindanao Island</t>
+  </si>
+  <si>
+    <t>Juan Carlos T. Gonzalez</t>
+  </si>
+  <si>
+    <t>MNH 3667</t>
+  </si>
+  <si>
+    <t>26.49 g</t>
+  </si>
+  <si>
+    <t>MNH 3666</t>
+  </si>
+  <si>
+    <t>26.3 g</t>
+  </si>
+  <si>
+    <t>MNH 3665</t>
+  </si>
+  <si>
+    <t>26.62 g</t>
+  </si>
+  <si>
+    <t>MNH 3664</t>
+  </si>
+  <si>
+    <t>29.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3663</t>
+  </si>
+  <si>
+    <t>Matam, Katipunan, Zamboanga, Mindanao Island</t>
+  </si>
+  <si>
+    <t>MNH 3662</t>
+  </si>
+  <si>
+    <t>Mt. Capoto-an, Samar Island</t>
+  </si>
+  <si>
+    <t>22.9 g; broken bills</t>
+  </si>
+  <si>
+    <t>MNH 3661</t>
+  </si>
+  <si>
+    <t>21.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3660</t>
+  </si>
+  <si>
+    <t>22.7 g</t>
+  </si>
+  <si>
+    <t>MNH 3659</t>
+  </si>
+  <si>
+    <t>23.8 g</t>
+  </si>
+  <si>
+    <t>MNH 3658</t>
+  </si>
+  <si>
+    <t>Matuguinao, Samar Island</t>
+  </si>
+  <si>
+    <t>MNH 3657</t>
+  </si>
+  <si>
+    <t>San Isidro, Samar Island</t>
+  </si>
+  <si>
+    <t>23.6 g</t>
+  </si>
+  <si>
+    <t>MNH 3656</t>
+  </si>
+  <si>
+    <t>24.9 g</t>
   </si>
 </sst>
 </file>
@@ -364,13 +949,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6E63DFA-8AA6-B547-9F17-DE05A6E7BB53}">
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:X137"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
@@ -2801,7 +3385,7 @@
       <c r="T30" s="2">
         <v>67.7</v>
       </c>
-      <c r="U30" s="5">
+      <c r="U30" s="2">
         <v>83</v>
       </c>
       <c r="V30" s="2"/>
@@ -2869,7 +3453,7 @@
       <c r="T31" s="2">
         <v>68</v>
       </c>
-      <c r="U31" s="5">
+      <c r="U31" s="2">
         <v>83.6</v>
       </c>
       <c r="V31" s="2"/>
@@ -3016,6 +3600,7622 @@
         <v>34</v>
       </c>
     </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="3">
+        <v>22742</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M34" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="N34" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O34" s="2">
+        <v>6</v>
+      </c>
+      <c r="P34" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R34" s="2">
+        <v>82</v>
+      </c>
+      <c r="S34" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="T34" s="2">
+        <v>53.6</v>
+      </c>
+      <c r="U34" s="2">
+        <v>76.400000000000006</v>
+      </c>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H35" s="3">
+        <v>22740</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="M35" s="2">
+        <v>10</v>
+      </c>
+      <c r="N35" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P35" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>19</v>
+      </c>
+      <c r="R35" s="2">
+        <v>81</v>
+      </c>
+      <c r="S35" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="T35" s="2">
+        <v>52.6</v>
+      </c>
+      <c r="U35" s="2">
+        <v>71.3</v>
+      </c>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H36" s="3">
+        <v>22737</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L36" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M36" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="N36" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O36" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="P36" s="2">
+        <v>12.2</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>20.8</v>
+      </c>
+      <c r="R36" s="2">
+        <v>83</v>
+      </c>
+      <c r="S36" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="T36" s="2">
+        <v>54.6</v>
+      </c>
+      <c r="U36" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="X36" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37" s="3">
+        <v>22762</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L37" s="2">
+        <v>15.3</v>
+      </c>
+      <c r="M37" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="N37" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O37" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="P37" s="2">
+        <v>11.7</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>17</v>
+      </c>
+      <c r="R37" s="2">
+        <v>84</v>
+      </c>
+      <c r="S37" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="T37" s="2">
+        <v>55.6</v>
+      </c>
+      <c r="U37" s="2">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="X37" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H38" s="3">
+        <v>22757</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L38" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="M38" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="N38" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O38" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P38" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="R38" s="2">
+        <v>76</v>
+      </c>
+      <c r="S38" s="2">
+        <v>32.1</v>
+      </c>
+      <c r="T38" s="2">
+        <v>43.9</v>
+      </c>
+      <c r="U38" s="2">
+        <v>67.3</v>
+      </c>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" s="3">
+        <v>22742</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L39" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="M39" s="2">
+        <v>10.4</v>
+      </c>
+      <c r="N39" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O39" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="P39" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>17.3</v>
+      </c>
+      <c r="R39" s="2">
+        <v>85</v>
+      </c>
+      <c r="S39" s="2">
+        <v>30.2</v>
+      </c>
+      <c r="T39" s="2">
+        <v>54.8</v>
+      </c>
+      <c r="U39" s="2">
+        <v>74.8</v>
+      </c>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H40" s="3">
+        <v>24642</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L40" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="M40" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="N40" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O40" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P40" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="R40" s="2">
+        <v>78</v>
+      </c>
+      <c r="S40" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="T40" s="2">
+        <v>58.7</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W40" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H41" s="3">
+        <v>24642</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L41" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="M41" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N41" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O41" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P41" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="R41" s="2">
+        <v>78</v>
+      </c>
+      <c r="S41" s="2">
+        <v>23.4</v>
+      </c>
+      <c r="T41" s="2">
+        <v>54.6</v>
+      </c>
+      <c r="U41" s="2">
+        <v>67.900000000000006</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W41" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="X41" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H42" s="3">
+        <v>24637</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L42" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="M42" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N42" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O42" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P42" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="R42" s="2">
+        <v>76</v>
+      </c>
+      <c r="S42" s="2">
+        <v>27.7</v>
+      </c>
+      <c r="T42" s="2">
+        <v>48.3</v>
+      </c>
+      <c r="U42" s="2">
+        <v>68.2</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H43" s="3">
+        <v>24255</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L43" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="M43" s="2">
+        <v>9</v>
+      </c>
+      <c r="N43" s="2">
+        <v>4</v>
+      </c>
+      <c r="O43" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P43" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="Q43" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="R43" s="2">
+        <v>79</v>
+      </c>
+      <c r="S43" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="T43" s="2">
+        <v>60.5</v>
+      </c>
+      <c r="U43" s="2">
+        <v>60.5</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="X43" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H44" s="3">
+        <v>23417</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L44" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="M44" s="2">
+        <v>7.8</v>
+      </c>
+      <c r="N44" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="O44" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P44" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="Q44" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="R44" s="2">
+        <v>77</v>
+      </c>
+      <c r="S44" s="2">
+        <v>20.3</v>
+      </c>
+      <c r="T44" s="2">
+        <v>56.7</v>
+      </c>
+      <c r="U44" s="2">
+        <v>62.8</v>
+      </c>
+      <c r="V44" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H45" s="3">
+        <v>23382</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="M45" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N45" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O45" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P45" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>12.8</v>
+      </c>
+      <c r="R45" s="2">
+        <v>78</v>
+      </c>
+      <c r="S45" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="T45" s="2">
+        <v>53.1</v>
+      </c>
+      <c r="U45" s="2">
+        <v>64.7</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W45" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X45" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H46" s="3">
+        <v>23381</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L46" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="M46" s="2">
+        <v>9</v>
+      </c>
+      <c r="N46" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P46" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="R46" s="2">
+        <v>86</v>
+      </c>
+      <c r="S46" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="T46" s="2">
+        <v>67.5</v>
+      </c>
+      <c r="U46" s="2">
+        <v>66.3</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="X46" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H47" s="3">
+        <v>23334</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L47" s="4">
+        <v>13.2</v>
+      </c>
+      <c r="M47" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N47" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O47" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P47" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>13.3</v>
+      </c>
+      <c r="R47" s="2">
+        <v>77</v>
+      </c>
+      <c r="S47" s="2">
+        <v>22</v>
+      </c>
+      <c r="T47" s="2">
+        <v>55</v>
+      </c>
+      <c r="U47" s="2">
+        <v>57.5</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H48" s="3">
+        <v>23323</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L48" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="M48" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="N48" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O48" s="2">
+        <v>5</v>
+      </c>
+      <c r="P48" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>12.1</v>
+      </c>
+      <c r="R48" s="2">
+        <v>80</v>
+      </c>
+      <c r="S48" s="2">
+        <v>23.7</v>
+      </c>
+      <c r="T48" s="2">
+        <v>56.3</v>
+      </c>
+      <c r="U48" s="2">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H49" s="3">
+        <v>23320</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="M49" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="N49" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="O49" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="P49" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="R49" s="2">
+        <v>76</v>
+      </c>
+      <c r="S49" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="T49" s="2">
+        <v>60.4</v>
+      </c>
+      <c r="U49" s="2">
+        <v>62.7</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H50" s="3">
+        <v>19114</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L50" s="4">
+        <v>12.9</v>
+      </c>
+      <c r="M50" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N50" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="O50" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="P50" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>14</v>
+      </c>
+      <c r="R50" s="2">
+        <v>75</v>
+      </c>
+      <c r="S50" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="T50" s="2">
+        <v>55.3</v>
+      </c>
+      <c r="U50" s="2">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H51" s="3">
+        <v>23123</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L51" s="2">
+        <v>13.7</v>
+      </c>
+      <c r="M51" s="2">
+        <v>9</v>
+      </c>
+      <c r="N51" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P51" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="R51" s="2">
+        <v>73</v>
+      </c>
+      <c r="S51" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="T51" s="2">
+        <v>57.6</v>
+      </c>
+      <c r="U51" s="2">
+        <v>68.3</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W51" s="2"/>
+      <c r="X51" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H52" s="3">
+        <v>22742</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L52" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="M52" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="N52" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O52" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="P52" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="Q52" s="2">
+        <v>13.3</v>
+      </c>
+      <c r="R52" s="2">
+        <v>90</v>
+      </c>
+      <c r="S52" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="T52" s="2">
+        <v>64.5</v>
+      </c>
+      <c r="U52" s="2">
+        <v>75</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H53" s="3">
+        <v>28521</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L53" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M53" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N53" s="2">
+        <v>4</v>
+      </c>
+      <c r="O53" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P53" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="R53" s="2">
+        <v>88</v>
+      </c>
+      <c r="S53" s="2">
+        <v>23.6</v>
+      </c>
+      <c r="T53" s="2">
+        <v>64.400000000000006</v>
+      </c>
+      <c r="U53" s="2">
+        <v>80</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W53" s="2"/>
+      <c r="X53" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H54" s="3">
+        <v>22737</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L54" s="2">
+        <v>17</v>
+      </c>
+      <c r="M54" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N54" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O54" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P54" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="R54" s="2">
+        <v>80</v>
+      </c>
+      <c r="S54" s="2">
+        <v>24</v>
+      </c>
+      <c r="T54" s="2">
+        <v>56</v>
+      </c>
+      <c r="U54" s="2">
+        <v>75</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W54" s="2"/>
+      <c r="X54" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H55" s="3">
+        <v>22763</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L55" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="M55" s="2">
+        <v>10</v>
+      </c>
+      <c r="N55" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O55" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P55" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="R55" s="2">
+        <v>85</v>
+      </c>
+      <c r="S55" s="2">
+        <v>26.1</v>
+      </c>
+      <c r="T55" s="2">
+        <v>58.9</v>
+      </c>
+      <c r="U55" s="2">
+        <v>90</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W55" s="2"/>
+      <c r="X55" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H56" s="3">
+        <v>22743</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L56" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="M56" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="N56" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P56" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="Q56" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="R56" s="2">
+        <v>90</v>
+      </c>
+      <c r="S56" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="T56" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="U56" s="2">
+        <v>82</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H57" s="3">
+        <v>24642</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L57" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="M57" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N57" s="2">
+        <v>4</v>
+      </c>
+      <c r="O57" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="P57" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="Q57" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="R57" s="2">
+        <v>83</v>
+      </c>
+      <c r="S57" s="2">
+        <v>23.1</v>
+      </c>
+      <c r="T57" s="2">
+        <v>59.9</v>
+      </c>
+      <c r="U57" s="2">
+        <v>83</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H58" s="3">
+        <v>24652</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L58" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="M58" s="2">
+        <v>8</v>
+      </c>
+      <c r="N58" s="2">
+        <v>3.9</v>
+      </c>
+      <c r="O58" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P58" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="Q58" s="2">
+        <v>15</v>
+      </c>
+      <c r="R58" s="2">
+        <v>75</v>
+      </c>
+      <c r="S58" s="2">
+        <v>20.3</v>
+      </c>
+      <c r="T58" s="2">
+        <v>54.7</v>
+      </c>
+      <c r="U58" s="2">
+        <v>76</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H59" s="3">
+        <v>25376</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L59" s="2">
+        <v>15</v>
+      </c>
+      <c r="M59" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N59" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O59" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P59" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q59" s="2">
+        <v>13.5</v>
+      </c>
+      <c r="R59" s="2">
+        <v>83</v>
+      </c>
+      <c r="S59" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="T59" s="2">
+        <v>57.5</v>
+      </c>
+      <c r="U59" s="2">
+        <v>75</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W59" s="2"/>
+      <c r="X59" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H60" s="3">
+        <v>22737</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L60" s="2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="M60" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="N60" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O60" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P60" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="Q60" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="R60" s="2">
+        <v>92</v>
+      </c>
+      <c r="S60" s="2">
+        <v>26.8</v>
+      </c>
+      <c r="T60" s="2">
+        <v>65.2</v>
+      </c>
+      <c r="U60" s="2">
+        <v>76</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H61" s="3">
+        <v>22738</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L61" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="M61" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N61" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O61" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P61" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Q61" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="R61" s="2">
+        <v>86</v>
+      </c>
+      <c r="S61" s="2">
+        <v>23.5</v>
+      </c>
+      <c r="T61" s="2">
+        <v>62.5</v>
+      </c>
+      <c r="U61" s="2">
+        <v>80</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H62" s="3">
+        <v>23417</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L62" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="M62" s="2">
+        <v>7.4</v>
+      </c>
+      <c r="N62" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O62" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P62" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="Q62" s="2">
+        <v>11.6</v>
+      </c>
+      <c r="R62" s="2">
+        <v>78</v>
+      </c>
+      <c r="S62" s="2">
+        <v>20.7</v>
+      </c>
+      <c r="T62" s="2">
+        <v>57.3</v>
+      </c>
+      <c r="U62" s="2">
+        <v>80</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W62" s="2"/>
+      <c r="X62" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H63" s="3">
+        <v>23944</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L63" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="M63" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="N63" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O63" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P63" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="R63" s="2">
+        <v>79</v>
+      </c>
+      <c r="S63" s="2">
+        <v>21.1</v>
+      </c>
+      <c r="T63" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="U63" s="2">
+        <v>87</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W63" s="2"/>
+      <c r="X63" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H64" s="3">
+        <v>24246</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L64" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="M64" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N64" s="2">
+        <v>4</v>
+      </c>
+      <c r="O64" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P64" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="R64" s="2">
+        <v>84</v>
+      </c>
+      <c r="S64" s="2">
+        <v>20.6</v>
+      </c>
+      <c r="T64" s="2">
+        <v>63.4</v>
+      </c>
+      <c r="U64" s="2">
+        <v>85</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W64" s="2"/>
+      <c r="X64" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H65" s="3">
+        <v>24248</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L65" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="M65" s="2">
+        <v>9</v>
+      </c>
+      <c r="N65" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O65" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P65" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>11.4</v>
+      </c>
+      <c r="R65" s="2">
+        <v>81</v>
+      </c>
+      <c r="S65" s="2">
+        <v>21.3</v>
+      </c>
+      <c r="T65" s="2">
+        <v>59.7</v>
+      </c>
+      <c r="U65" s="2">
+        <v>81</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W65" s="2"/>
+      <c r="X65" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H66" s="3">
+        <v>23348</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L66" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="M66" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N66" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O66" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P66" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>15</v>
+      </c>
+      <c r="R66" s="2">
+        <v>80</v>
+      </c>
+      <c r="S66" s="2">
+        <v>25.2</v>
+      </c>
+      <c r="T66" s="2">
+        <v>54.8</v>
+      </c>
+      <c r="U66" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W66" s="2"/>
+      <c r="X66" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H67" s="3">
+        <v>23369</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L67" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M67" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N67" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O67" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P67" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>13.3</v>
+      </c>
+      <c r="R67" s="2">
+        <v>78</v>
+      </c>
+      <c r="S67" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="T67" s="2">
+        <v>60.8</v>
+      </c>
+      <c r="U67" s="2">
+        <v>85</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W67" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="X67" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H68" s="3">
+        <v>23371</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L68" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="M68" s="2">
+        <v>9</v>
+      </c>
+      <c r="N68" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O68" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P68" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="R68" s="2">
+        <v>79</v>
+      </c>
+      <c r="S68" s="2">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="T68" s="2">
+        <v>59.1</v>
+      </c>
+      <c r="U68" s="2">
+        <v>80</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H69" s="3">
+        <v>23378</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L69" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="M69" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N69" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P69" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>13.4</v>
+      </c>
+      <c r="R69" s="2">
+        <v>87</v>
+      </c>
+      <c r="S69" s="2">
+        <v>18.2</v>
+      </c>
+      <c r="T69" s="2">
+        <v>68.8</v>
+      </c>
+      <c r="U69" s="2">
+        <v>80</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W69" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H70" s="3">
+        <v>23380</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L70" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="M70" s="2">
+        <v>8</v>
+      </c>
+      <c r="N70" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P70" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>13</v>
+      </c>
+      <c r="R70" s="2">
+        <v>80</v>
+      </c>
+      <c r="S70" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="T70" s="2">
+        <v>61.4</v>
+      </c>
+      <c r="U70" s="2">
+        <v>87</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W70" s="2"/>
+      <c r="X70" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H71" s="3">
+        <v>23124</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L71" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M71" s="2">
+        <v>7.7</v>
+      </c>
+      <c r="N71" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O71" s="2">
+        <v>5.7</v>
+      </c>
+      <c r="P71" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="R71" s="2">
+        <v>81</v>
+      </c>
+      <c r="S71" s="2">
+        <v>22.9</v>
+      </c>
+      <c r="T71" s="2">
+        <v>58.1</v>
+      </c>
+      <c r="U71" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W71" s="2"/>
+      <c r="X71" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H72" s="3">
+        <v>23104</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L72" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="M72" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N72" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P72" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="R72" s="2">
+        <v>79</v>
+      </c>
+      <c r="S72" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="T72" s="2">
+        <v>59.7</v>
+      </c>
+      <c r="U72" s="2">
+        <v>85</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W72" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H73" s="3">
+        <v>24920</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L73" s="4">
+        <v>13.3</v>
+      </c>
+      <c r="M73" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N73" s="2">
+        <v>5</v>
+      </c>
+      <c r="O73" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="P73" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="R73" s="2">
+        <v>76.900000000000006</v>
+      </c>
+      <c r="S73" s="2">
+        <v>34.299999999999997</v>
+      </c>
+      <c r="T73" s="2">
+        <v>42.6</v>
+      </c>
+      <c r="U73" s="2">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W73" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X73" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H74" s="3">
+        <v>24946</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L74" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="M74" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N74" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O74" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P74" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="R74" s="2">
+        <v>77.7</v>
+      </c>
+      <c r="S74" s="2">
+        <v>38</v>
+      </c>
+      <c r="T74" s="2">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="U74" s="2">
+        <v>81</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H75" s="3">
+        <v>24954</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L75" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="M75" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="N75" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O75" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P75" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="R75" s="2">
+        <v>79.5</v>
+      </c>
+      <c r="S75" s="2">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="T75" s="2">
+        <v>45.7</v>
+      </c>
+      <c r="U75" s="2">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W75" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X75" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H76" s="3">
+        <v>24954</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L76" s="4">
+        <v>13.6</v>
+      </c>
+      <c r="M76" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N76" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O76" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="P76" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="R76" s="2">
+        <v>73.7</v>
+      </c>
+      <c r="S76" s="2">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="T76" s="2">
+        <v>41</v>
+      </c>
+      <c r="U76" s="2">
+        <v>70.3</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W76" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="X76" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H77" s="3">
+        <v>24962</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L77" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="M77" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N77" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O77" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="P77" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="R77" s="2">
+        <v>76.8</v>
+      </c>
+      <c r="S77" s="2">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="T77" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="U77" s="2">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W77" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H78" s="3">
+        <v>24964</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L78" s="2">
+        <v>15.7</v>
+      </c>
+      <c r="M78" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N78" s="2">
+        <v>4</v>
+      </c>
+      <c r="O78" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P78" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>17</v>
+      </c>
+      <c r="R78" s="2">
+        <v>79</v>
+      </c>
+      <c r="S78" s="2">
+        <v>28.8</v>
+      </c>
+      <c r="T78" s="2">
+        <v>50.2</v>
+      </c>
+      <c r="U78" s="2">
+        <v>80.8</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X78" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H79" s="3">
+        <v>24970</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L79" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="M79" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N79" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O79" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P79" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="R79" s="2">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="S79" s="2">
+        <v>33</v>
+      </c>
+      <c r="T79" s="2">
+        <v>40.9</v>
+      </c>
+      <c r="U79" s="2">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W79" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X79" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H80" s="3">
+        <v>24977</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L80" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="M80" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N80" s="2">
+        <v>4</v>
+      </c>
+      <c r="O80" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P80" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="R80" s="2">
+        <v>80.8</v>
+      </c>
+      <c r="S80" s="2">
+        <v>31</v>
+      </c>
+      <c r="T80" s="2">
+        <v>49.8</v>
+      </c>
+      <c r="U80" s="2">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H81" s="3">
+        <v>24981</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L81" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="M81" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N81" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O81" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P81" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="R81" s="2">
+        <v>75.8</v>
+      </c>
+      <c r="S81" s="2">
+        <v>35</v>
+      </c>
+      <c r="T81" s="2">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="U81" s="2">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W81" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X81" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H82" s="3">
+        <v>24981</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L82" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="M82" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N82" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O82" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P82" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="R82" s="2">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="S82" s="2">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="T82" s="2">
+        <v>44.3</v>
+      </c>
+      <c r="U82" s="2">
+        <v>82.5</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W82" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L83" s="2">
+        <v>15</v>
+      </c>
+      <c r="M83" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N83" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O83" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P83" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R83" s="2">
+        <v>85.5</v>
+      </c>
+      <c r="S83" s="2">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="T83" s="2">
+        <v>51.8</v>
+      </c>
+      <c r="U83" s="2">
+        <v>75.5</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W83" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X83" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H84" s="3">
+        <v>25041</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L84" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M84" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N84" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O84" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P84" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R84" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="S84" s="2">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="T84" s="2">
+        <v>37.9</v>
+      </c>
+      <c r="U84" s="2">
+        <v>76.5</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W84" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X84" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H85" s="3">
+        <v>23103</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N85" s="2">
+        <v>4</v>
+      </c>
+      <c r="O85" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="P85" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q85" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="R85" s="2">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="S85" s="2">
+        <v>30.6</v>
+      </c>
+      <c r="T85" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="U85" s="2">
+        <v>74.099999999999994</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="X85" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="H86" s="3">
+        <v>23104</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L86" s="4">
+        <v>13.4</v>
+      </c>
+      <c r="M86" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N86" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O86" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P86" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R86" s="2">
+        <v>76.8</v>
+      </c>
+      <c r="S86" s="2">
+        <v>31.8</v>
+      </c>
+      <c r="T86" s="2">
+        <v>45</v>
+      </c>
+      <c r="U86" s="2">
+        <v>81.2</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W86" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="X86" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H87" s="3">
+        <v>24627</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L87" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="M87" s="2">
+        <v>9</v>
+      </c>
+      <c r="N87" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O87" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="P87" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q87" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="R87" s="2">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="S87" s="2">
+        <v>30.4</v>
+      </c>
+      <c r="T87" s="2">
+        <v>44.7</v>
+      </c>
+      <c r="U87" s="2">
+        <v>84.2</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="X87" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H88" s="3">
+        <v>24630</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L88" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="M88" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N88" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O88" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P88" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="R88" s="2">
+        <v>73.5</v>
+      </c>
+      <c r="S88" s="2">
+        <v>32.9</v>
+      </c>
+      <c r="T88" s="2">
+        <v>40.6</v>
+      </c>
+      <c r="U88" s="2">
+        <v>74</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H89" s="3">
+        <v>24630</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L89" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="M89" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N89" s="2">
+        <v>5</v>
+      </c>
+      <c r="O89" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="P89" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="Q89" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="R89" s="2">
+        <v>83</v>
+      </c>
+      <c r="S89" s="2">
+        <v>35.6</v>
+      </c>
+      <c r="T89" s="2">
+        <v>47.4</v>
+      </c>
+      <c r="U89" s="2">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W89" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="X89" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H90" s="3">
+        <v>24638</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L90" s="2">
+        <v>15</v>
+      </c>
+      <c r="M90" s="2">
+        <v>9</v>
+      </c>
+      <c r="N90" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O90" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P90" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q90" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R90" s="2">
+        <v>80.3</v>
+      </c>
+      <c r="S90" s="2">
+        <v>36.6</v>
+      </c>
+      <c r="T90" s="2">
+        <v>43.7</v>
+      </c>
+      <c r="U90" s="2">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W90" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H91" s="3">
+        <v>24642</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L91" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="M91" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N91" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O91" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P91" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>15.7</v>
+      </c>
+      <c r="R91" s="2">
+        <v>86</v>
+      </c>
+      <c r="S91" s="2">
+        <v>33.1</v>
+      </c>
+      <c r="T91" s="2">
+        <v>52.9</v>
+      </c>
+      <c r="U91" s="2">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W91" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="X91" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="H92" s="3">
+        <v>24680</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L92" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="M92" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N92" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O92" s="2">
+        <v>5</v>
+      </c>
+      <c r="P92" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q92" s="2">
+        <v>18.3</v>
+      </c>
+      <c r="R92" s="2">
+        <v>82.7</v>
+      </c>
+      <c r="S92" s="2">
+        <v>33.5</v>
+      </c>
+      <c r="T92" s="2">
+        <v>49.2</v>
+      </c>
+      <c r="U92" s="2">
+        <v>85.2</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H93" s="3">
+        <v>24907</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L93" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="M93" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="N93" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O93" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P93" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q93" s="2">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="R93" s="2">
+        <v>87.3</v>
+      </c>
+      <c r="S93" s="2">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="T93" s="2">
+        <v>53.5</v>
+      </c>
+      <c r="U93" s="2">
+        <v>83.8</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X93" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L94" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="M94" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="N94" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O94" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="P94" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Q94" s="2">
+        <v>17.8</v>
+      </c>
+      <c r="R94" s="2">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="S94" s="2">
+        <v>37.4</v>
+      </c>
+      <c r="T94" s="2">
+        <v>42.5</v>
+      </c>
+      <c r="U94" s="2">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W94" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H95" s="3">
+        <v>24245</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L95" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="M95" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="N95" s="2">
+        <v>5</v>
+      </c>
+      <c r="O95" s="2">
+        <v>5</v>
+      </c>
+      <c r="P95" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q95" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="R95" s="2">
+        <v>75.599999999999994</v>
+      </c>
+      <c r="S95" s="2">
+        <v>38.200000000000003</v>
+      </c>
+      <c r="T95" s="2">
+        <v>37.4</v>
+      </c>
+      <c r="U95" s="2">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="V95" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W95" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H96" s="3">
+        <v>24245</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L96" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="M96" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N96" s="2">
+        <v>5</v>
+      </c>
+      <c r="O96" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P96" s="2">
+        <v>11.1</v>
+      </c>
+      <c r="Q96" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="R96" s="2">
+        <v>75.5</v>
+      </c>
+      <c r="S96" s="2">
+        <v>39.9</v>
+      </c>
+      <c r="T96" s="2">
+        <v>35.6</v>
+      </c>
+      <c r="U96" s="2">
+        <v>77.2</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="H97" s="3">
+        <v>24249</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L97" s="2">
+        <v>14</v>
+      </c>
+      <c r="M97" s="2">
+        <v>7.6</v>
+      </c>
+      <c r="N97" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O97" s="2">
+        <v>5</v>
+      </c>
+      <c r="P97" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="Q97" s="2">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="R97" s="2">
+        <v>80.8</v>
+      </c>
+      <c r="S97" s="2">
+        <v>32.6</v>
+      </c>
+      <c r="T97" s="2">
+        <v>48.2</v>
+      </c>
+      <c r="U97" s="2">
+        <v>76.3</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="H98" s="3">
+        <v>24249</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L98" s="4">
+        <v>13.4</v>
+      </c>
+      <c r="M98" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="N98" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O98" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P98" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q98" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="R98" s="2">
+        <v>76.3</v>
+      </c>
+      <c r="S98" s="2">
+        <v>34.4</v>
+      </c>
+      <c r="T98" s="2">
+        <v>41.9</v>
+      </c>
+      <c r="U98" s="2">
+        <v>82.7</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W98" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H99" s="3">
+        <v>24251</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L99" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="M99" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="N99" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O99" s="2">
+        <v>5</v>
+      </c>
+      <c r="P99" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q99" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="R99" s="2">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="S99" s="2">
+        <v>39.5</v>
+      </c>
+      <c r="T99" s="2">
+        <v>41.1</v>
+      </c>
+      <c r="U99" s="2">
+        <v>79.2</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W99" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="X99" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H100" s="3">
+        <v>24255</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L100" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M100" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N100" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O100" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P100" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q100" s="2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R100" s="2">
+        <v>76.8</v>
+      </c>
+      <c r="S100" s="2">
+        <v>34.6</v>
+      </c>
+      <c r="T100" s="2">
+        <v>42.2</v>
+      </c>
+      <c r="U100" s="2">
+        <v>77.599999999999994</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W100" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H101" s="3">
+        <v>24257</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L101" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="M101" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="N101" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O101" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="P101" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="Q101" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="R101" s="2">
+        <v>76.5</v>
+      </c>
+      <c r="S101" s="2">
+        <v>30.7</v>
+      </c>
+      <c r="T101" s="2">
+        <v>45.8</v>
+      </c>
+      <c r="U101" s="2">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W101" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H102" s="3">
+        <v>24257</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L102" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="M102" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N102" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O102" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P102" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q102" s="2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="R102" s="2">
+        <v>81.5</v>
+      </c>
+      <c r="S102" s="2">
+        <v>29.6</v>
+      </c>
+      <c r="T102" s="2">
+        <v>51.9</v>
+      </c>
+      <c r="U102" s="2">
+        <v>75.400000000000006</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W102" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="X102" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H103" s="3">
+        <v>23898</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L103" s="2">
+        <v>14</v>
+      </c>
+      <c r="M103" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N103" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O103" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P103" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q103" s="2">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="R103" s="2">
+        <v>77.5</v>
+      </c>
+      <c r="S103" s="2">
+        <v>33.9</v>
+      </c>
+      <c r="T103" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="U103" s="2">
+        <v>79.7</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H104" s="3">
+        <v>23897</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L104" s="4">
+        <v>13.7</v>
+      </c>
+      <c r="M104" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="N104" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O104" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="P104" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q104" s="2">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="R104" s="2">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="S104" s="2">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="T104" s="2">
+        <v>40.9</v>
+      </c>
+      <c r="U104" s="2">
+        <v>75.2</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H105" s="3">
+        <v>23869</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L105" s="2">
+        <v>14.1</v>
+      </c>
+      <c r="M105" s="2">
+        <v>9</v>
+      </c>
+      <c r="N105" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="O105" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="P105" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q105" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="R105" s="2">
+        <v>81.3</v>
+      </c>
+      <c r="S105" s="2">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="T105" s="2">
+        <v>43.6</v>
+      </c>
+      <c r="U105" s="2">
+        <v>74</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W105" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H106" s="3">
+        <v>23501</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L106" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="M106" s="2">
+        <v>10.1</v>
+      </c>
+      <c r="N106" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O106" s="2">
+        <v>5</v>
+      </c>
+      <c r="P106" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="Q106" s="2">
+        <v>16.3</v>
+      </c>
+      <c r="R106" s="2">
+        <v>76.8</v>
+      </c>
+      <c r="S106" s="2">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="T106" s="2">
+        <v>41.6</v>
+      </c>
+      <c r="U106" s="2">
+        <v>76.2</v>
+      </c>
+      <c r="V106" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W106" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X106" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H107" s="3">
+        <v>23378</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L107" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="M107" s="2">
+        <v>9</v>
+      </c>
+      <c r="N107" s="2">
+        <v>5</v>
+      </c>
+      <c r="O107" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P107" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q107" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="R107" s="2">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="S107" s="2">
+        <v>30.3</v>
+      </c>
+      <c r="T107" s="2">
+        <v>48.6</v>
+      </c>
+      <c r="U107" s="2">
+        <v>74.2</v>
+      </c>
+      <c r="V107" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W107" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X107" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H108" s="3">
+        <v>23375</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L108" s="2">
+        <v>13.9</v>
+      </c>
+      <c r="M108" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N108" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O108" s="2">
+        <v>5</v>
+      </c>
+      <c r="P108" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q108" s="2">
+        <v>17.7</v>
+      </c>
+      <c r="R108" s="2">
+        <v>82.6</v>
+      </c>
+      <c r="S108" s="2">
+        <v>38</v>
+      </c>
+      <c r="T108" s="2">
+        <v>44.6</v>
+      </c>
+      <c r="U108" s="2">
+        <v>80.8</v>
+      </c>
+      <c r="V108" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W108" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="X108" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H109" s="3">
+        <v>23373</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N109" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O109" s="2">
+        <v>5</v>
+      </c>
+      <c r="P109" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q109" s="2">
+        <v>17.2</v>
+      </c>
+      <c r="R109" s="2">
+        <v>82.2</v>
+      </c>
+      <c r="S109" s="2">
+        <v>32.6</v>
+      </c>
+      <c r="T109" s="2">
+        <v>49.6</v>
+      </c>
+      <c r="U109" s="2">
+        <v>79.5</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="X109" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H110" s="3">
+        <v>23368</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N110" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="O110" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P110" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="Q110" s="2">
+        <v>18.2</v>
+      </c>
+      <c r="R110" s="2">
+        <v>81.7</v>
+      </c>
+      <c r="S110" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="T110" s="2">
+        <v>50.2</v>
+      </c>
+      <c r="U110" s="2">
+        <v>78.5</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="H111" s="3">
+        <v>23348</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L111" s="2">
+        <v>13.8</v>
+      </c>
+      <c r="M111" s="2">
+        <v>8</v>
+      </c>
+      <c r="N111" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O111" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P111" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="Q111" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="R111" s="2">
+        <v>81.7</v>
+      </c>
+      <c r="S111" s="2">
+        <v>32.1</v>
+      </c>
+      <c r="T111" s="2">
+        <v>49.6</v>
+      </c>
+      <c r="U111" s="2">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H112" s="3">
+        <v>23153</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L112" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="M112" s="2">
+        <v>9</v>
+      </c>
+      <c r="N112" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O112" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="P112" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="Q112" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="R112" s="2">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="S112" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="T112" s="2">
+        <v>49.4</v>
+      </c>
+      <c r="U112" s="2">
+        <v>76.2</v>
+      </c>
+      <c r="V112" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="H113" s="3">
+        <v>23337</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L113" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M113" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="N113" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="O113" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P113" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q113" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="R113" s="2">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="S113" s="2">
+        <v>33</v>
+      </c>
+      <c r="T113" s="2">
+        <v>46.1</v>
+      </c>
+      <c r="U113" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H114" s="3">
+        <v>23334</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L114" s="2">
+        <v>14.9</v>
+      </c>
+      <c r="M114" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="N114" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O114" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P114" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q114" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="R114" s="2">
+        <v>80.5</v>
+      </c>
+      <c r="S114" s="2">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="T114" s="2">
+        <v>46.8</v>
+      </c>
+      <c r="U114" s="2">
+        <v>77.900000000000006</v>
+      </c>
+      <c r="V114" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H115" s="3">
+        <v>23330</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L115" s="2">
+        <v>14.6</v>
+      </c>
+      <c r="M115" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N115" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="O115" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P115" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="Q115" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="R115" s="2">
+        <v>68.2</v>
+      </c>
+      <c r="S115" s="2">
+        <v>30.4</v>
+      </c>
+      <c r="T115" s="2">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="U115" s="2">
+        <v>81</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H116" s="3">
+        <v>23323</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L116" s="2">
+        <v>14</v>
+      </c>
+      <c r="M116" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="N116" s="2">
+        <v>5</v>
+      </c>
+      <c r="O116" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P116" s="2">
+        <v>10.7</v>
+      </c>
+      <c r="Q116" s="2">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="R116" s="2">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="S116" s="2">
+        <v>28.6</v>
+      </c>
+      <c r="T116" s="2">
+        <v>53</v>
+      </c>
+      <c r="U116" s="2">
+        <v>80.3</v>
+      </c>
+      <c r="V116" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W116" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X116" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A117" s="2">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="H117" s="3">
+        <v>23146</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L117" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="M117" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N117" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O117" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P117" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q117" s="2">
+        <v>17.5</v>
+      </c>
+      <c r="R117" s="2">
+        <v>85.3</v>
+      </c>
+      <c r="S117" s="2">
+        <v>27.1</v>
+      </c>
+      <c r="T117" s="2">
+        <v>58.2</v>
+      </c>
+      <c r="U117" s="2">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="V117" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H118" s="3">
+        <v>23118</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L118" s="4">
+        <v>13.3</v>
+      </c>
+      <c r="M118" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N118" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O118" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P118" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Q118" s="2">
+        <v>20.2</v>
+      </c>
+      <c r="R118" s="2">
+        <v>77.5</v>
+      </c>
+      <c r="S118" s="2">
+        <v>30.2</v>
+      </c>
+      <c r="T118" s="2">
+        <v>47.3</v>
+      </c>
+      <c r="U118" s="2">
+        <v>78.900000000000006</v>
+      </c>
+      <c r="V118" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W118" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="X118" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A119" s="2">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H119" s="3">
+        <v>23104</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L119" s="2">
+        <v>14</v>
+      </c>
+      <c r="M119" s="2">
+        <v>8.1</v>
+      </c>
+      <c r="N119" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O119" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="P119" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q119" s="2">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="R119" s="2">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="S119" s="2">
+        <v>32.9</v>
+      </c>
+      <c r="T119" s="2">
+        <v>47.7</v>
+      </c>
+      <c r="U119" s="2">
+        <v>81.2</v>
+      </c>
+      <c r="V119" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="X119" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A120" s="2">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H120" s="3">
+        <v>23115</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L120" s="4">
+        <v>13.4</v>
+      </c>
+      <c r="M120" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N120" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O120" s="2">
+        <v>5.2</v>
+      </c>
+      <c r="P120" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="Q120" s="2">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R120" s="2">
+        <v>81.7</v>
+      </c>
+      <c r="S120" s="2">
+        <v>29.4</v>
+      </c>
+      <c r="T120" s="2">
+        <v>52.3</v>
+      </c>
+      <c r="U120" s="2">
+        <v>80</v>
+      </c>
+      <c r="V120" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W120" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="X120" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A121" s="2">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H121" s="3">
+        <v>23108</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L121" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="M121" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N121" s="2">
+        <v>4</v>
+      </c>
+      <c r="O121" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P121" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q121" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="R121" s="2">
+        <v>82.1</v>
+      </c>
+      <c r="S121" s="2">
+        <v>29.8</v>
+      </c>
+      <c r="T121" s="2">
+        <v>52.3</v>
+      </c>
+      <c r="U121" s="2">
+        <v>79.3</v>
+      </c>
+      <c r="V121" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W121" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A122" s="2">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H122" s="3">
+        <v>23106</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L122" s="4">
+        <v>13.7</v>
+      </c>
+      <c r="M122" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="N122" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O122" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P122" s="2">
+        <v>10.8</v>
+      </c>
+      <c r="Q122" s="2">
+        <v>17.3</v>
+      </c>
+      <c r="R122" s="2">
+        <v>80.3</v>
+      </c>
+      <c r="S122" s="2">
+        <v>33.6</v>
+      </c>
+      <c r="T122" s="2">
+        <v>46.7</v>
+      </c>
+      <c r="U122" s="2">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A123" s="2">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H123" s="3">
+        <v>23105</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L123" s="4">
+        <v>13.7</v>
+      </c>
+      <c r="M123" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N123" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="O123" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P123" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="Q123" s="2">
+        <v>16.8</v>
+      </c>
+      <c r="R123" s="2">
+        <v>79.5</v>
+      </c>
+      <c r="S123" s="2">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T123" s="2">
+        <v>46.2</v>
+      </c>
+      <c r="U123" s="2">
+        <v>83</v>
+      </c>
+      <c r="V123" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="X123" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A124" s="2">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H124" s="3">
+        <v>23104</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L124" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="M124" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="N124" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O124" s="2">
+        <v>4.7</v>
+      </c>
+      <c r="P124" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="Q124" s="2">
+        <v>18</v>
+      </c>
+      <c r="R124" s="2">
+        <v>74.7</v>
+      </c>
+      <c r="S124" s="2">
+        <v>24.1</v>
+      </c>
+      <c r="T124" s="2">
+        <v>50.6</v>
+      </c>
+      <c r="U124" s="2">
+        <v>79.3</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W124" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A125" s="2">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H125" s="3">
+        <v>23923</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L125" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="M125" s="2">
+        <v>10</v>
+      </c>
+      <c r="N125" s="2">
+        <v>4.8</v>
+      </c>
+      <c r="O125" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="P125" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="Q125" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="R125" s="2">
+        <v>87.4</v>
+      </c>
+      <c r="S125" s="2">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="T125" s="2">
+        <v>52.7</v>
+      </c>
+      <c r="U125" s="2">
+        <v>79.2</v>
+      </c>
+      <c r="V125" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W125" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H126" s="3">
+        <v>23104</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L126" s="2">
+        <v>14.8</v>
+      </c>
+      <c r="M126" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="N126" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O126" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="P126" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="Q126" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="R126" s="2">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="S126" s="2">
+        <v>34.1</v>
+      </c>
+      <c r="T126" s="2">
+        <v>43</v>
+      </c>
+      <c r="U126" s="2">
+        <v>78.3</v>
+      </c>
+      <c r="V126" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A127" s="2">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H127" s="3">
+        <v>23103</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L127" s="2">
+        <v>15</v>
+      </c>
+      <c r="M127" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="N127" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O127" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P127" s="2">
+        <v>10.7</v>
+      </c>
+      <c r="Q127" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="R127" s="2">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="S127" s="2">
+        <v>31.7</v>
+      </c>
+      <c r="T127" s="2">
+        <v>42.9</v>
+      </c>
+      <c r="U127" s="2">
+        <v>60.8</v>
+      </c>
+      <c r="V127" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W127" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="X127" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H128" s="3">
+        <v>23103</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L128" s="2">
+        <v>14.2</v>
+      </c>
+      <c r="M128" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="N128" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="O128" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P128" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q128" s="2">
+        <v>18.8</v>
+      </c>
+      <c r="R128" s="2">
+        <v>82.4</v>
+      </c>
+      <c r="S128" s="2">
+        <v>33</v>
+      </c>
+      <c r="T128" s="2">
+        <v>49.4</v>
+      </c>
+      <c r="U128" s="2">
+        <v>81</v>
+      </c>
+      <c r="V128" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W128" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="X128" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A129" s="2">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H129" s="3">
+        <v>23102</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L129" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="M129" s="2">
+        <v>8</v>
+      </c>
+      <c r="N129" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="O129" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="P129" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q129" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="R129" s="2">
+        <v>83.1</v>
+      </c>
+      <c r="S129" s="2">
+        <v>26.3</v>
+      </c>
+      <c r="T129" s="2">
+        <v>56.8</v>
+      </c>
+      <c r="U129" s="2">
+        <v>80.7</v>
+      </c>
+      <c r="V129" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A130" s="2">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H130" s="3">
+        <v>19140</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L130" s="4">
+        <v>13.5</v>
+      </c>
+      <c r="M130" s="2">
+        <v>7.9</v>
+      </c>
+      <c r="N130" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="O130" s="2">
+        <v>4</v>
+      </c>
+      <c r="P130" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q130" s="2">
+        <v>17.3</v>
+      </c>
+      <c r="R130" s="2">
+        <v>67.8</v>
+      </c>
+      <c r="S130" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="T130" s="2">
+        <v>47.7</v>
+      </c>
+      <c r="U130" s="2">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="V130" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="W130" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="X130" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A131" s="2">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H131" s="3">
+        <v>20955</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N131" s="2">
+        <v>3.3</v>
+      </c>
+      <c r="O131" s="2">
+        <v>5.3</v>
+      </c>
+      <c r="P131" s="2">
+        <v>11</v>
+      </c>
+      <c r="Q131" s="2">
+        <v>15.8</v>
+      </c>
+      <c r="R131" s="2">
+        <v>71.8</v>
+      </c>
+      <c r="S131" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="T131" s="2">
+        <v>51.3</v>
+      </c>
+      <c r="U131" s="2">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="V131" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W131" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="X131" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A132" s="2">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H132" s="3">
+        <v>20948</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L132" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="M132" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="N132" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="O132" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="P132" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="Q132" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="R132" s="2">
+        <v>71.599999999999994</v>
+      </c>
+      <c r="S132" s="2">
+        <v>25.1</v>
+      </c>
+      <c r="T132" s="2">
+        <v>46.5</v>
+      </c>
+      <c r="U132" s="2">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="V132" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W132" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="X132" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A133" s="2">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H133" s="3">
+        <v>20948</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L133" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="M133" s="2">
+        <v>8.6</v>
+      </c>
+      <c r="N133" s="2">
+        <v>4</v>
+      </c>
+      <c r="O133" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="P133" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="Q133" s="2">
+        <v>18.2</v>
+      </c>
+      <c r="R133" s="2">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="S133" s="2">
+        <v>24.7</v>
+      </c>
+      <c r="T133" s="2">
+        <v>45.9</v>
+      </c>
+      <c r="U133" s="2">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="V133" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W133" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="X133" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A134" s="2">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H134" s="3">
+        <v>20946</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L134" s="2">
+        <v>13.1</v>
+      </c>
+      <c r="M134" s="2">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="N134" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="O134" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P134" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="Q134" s="2">
+        <v>15.2</v>
+      </c>
+      <c r="R134" s="2">
+        <v>75.7</v>
+      </c>
+      <c r="S134" s="2">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="T134" s="2">
+        <v>55.6</v>
+      </c>
+      <c r="U134" s="2">
+        <v>49.7</v>
+      </c>
+      <c r="V134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W134" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="X134" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A135" s="2">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="H135" s="3">
+        <v>20926</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L135" s="4">
+        <v>13.7</v>
+      </c>
+      <c r="M135" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="N135" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="O135" s="2">
+        <v>4.3</v>
+      </c>
+      <c r="P135" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q135" s="2">
+        <v>15.6</v>
+      </c>
+      <c r="R135" s="2">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="S135" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="T135" s="2">
+        <v>48</v>
+      </c>
+      <c r="U135" s="2">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="V135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W135" s="2">
+        <v>22.1</v>
+      </c>
+      <c r="X135" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A136" s="2">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H136" s="3">
+        <v>20942</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L136" s="2">
+        <v>14.3</v>
+      </c>
+      <c r="M136" s="2">
+        <v>9</v>
+      </c>
+      <c r="N136" s="2">
+        <v>4</v>
+      </c>
+      <c r="O136" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P136" s="2">
+        <v>9.1</v>
+      </c>
+      <c r="Q136" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="R136" s="2">
+        <v>80.900000000000006</v>
+      </c>
+      <c r="S136" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="T136" s="2">
+        <v>53.4</v>
+      </c>
+      <c r="U136" s="2">
+        <v>77.099999999999994</v>
+      </c>
+      <c r="V136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W136" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="X136" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A137" s="2">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H137" s="3">
+        <v>20938</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L137" s="2">
+        <v>15.1</v>
+      </c>
+      <c r="M137" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N137" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="O137" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="P137" s="2">
+        <v>10.7</v>
+      </c>
+      <c r="Q137" s="2">
+        <v>14.7</v>
+      </c>
+      <c r="R137" s="2">
+        <v>77.400000000000006</v>
+      </c>
+      <c r="S137" s="2">
+        <v>24.9</v>
+      </c>
+      <c r="T137" s="2">
+        <v>52.5</v>
+      </c>
+      <c r="U137" s="2">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="V137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W137" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="X137" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
